--- a/survey_templates/049_vet_course_preparation_survey--survey_templates.xlsx
+++ b/survey_templates/049_vet_course_preparation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'program_c'}</t>
+          <t>program_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Program C'}</t>
+          <t>Program C</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'twice'}</t>
+          <t>twice</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Twice'}</t>
+          <t>Twice</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_once'}</t>
+          <t>more_than_once</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'More than once'}</t>
+          <t>More than once</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'method_1'}</t>
+          <t>method_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Method 1'}</t>
+          <t>Method 1</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'method_2'}</t>
+          <t>method_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Method 2'}</t>
+          <t>Method 2</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'method_3'}</t>
+          <t>method_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Method 3'}</t>
+          <t>Method 3</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
